--- a/data/TTS/最新版班表/2026-10/TTS_TA.xlsx
+++ b/data/TTS/最新版班表/2026-10/TTS_TA.xlsx
@@ -1098,20 +1098,14 @@
 8:05</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LUT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -1170,12 +1164,9 @@
 9:38</t>
         </is>
       </c>
-      <c r="O8" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1199,12 +1190,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S8" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr">
@@ -1538,20 +1526,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1559,12 +1541,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1643,12 +1622,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="V10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W10" s="1" t="inlineStr">
@@ -1730,12 +1706,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1786,12 +1759,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M11" s="1" t="inlineStr">
@@ -1962,20 +1932,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1983,12 +1947,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
@@ -2070,12 +2031,9 @@
 8:30</t>
         </is>
       </c>
-      <c r="V12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2088,12 +2046,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2231,12 +2186,9 @@
 8:01</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2836,12 +2788,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="N16" s="1" t="inlineStr">
@@ -2852,12 +2801,9 @@
 8:18</t>
         </is>
       </c>
-      <c r="O16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2947,12 +2893,9 @@
 8:38</t>
         </is>
       </c>
-      <c r="AC16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="AD16" s="1" t="inlineStr">
@@ -2975,12 +2918,9 @@
           <t>叢君儀</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3350,12 +3290,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="AA18" s="1" t="inlineStr">
@@ -3751,12 +3688,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W20" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3764,12 +3698,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y20" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z20" s="1" t="inlineStr">
@@ -4400,20 +4331,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="AA23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4421,12 +4346,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4650,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -4781,12 +4700,9 @@
 8:18</t>
         </is>
       </c>
-      <c r="U25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V25" s="1" t="inlineStr">
@@ -4938,20 +4854,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="N26" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -5139,12 +5049,9 @@
 8:33</t>
         </is>
       </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -5202,12 +5109,9 @@
 8:03</t>
         </is>
       </c>
-      <c r="U27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -5215,12 +5119,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X27" s="1" t="inlineStr">
@@ -5686,12 +5587,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -5900,12 +5798,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD30" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6156,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W32" s="1" t="inlineStr">
@@ -6739,12 +6631,9 @@
 8:10</t>
         </is>
       </c>
-      <c r="AC34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -7545,12 +7434,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W38" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X38" s="1" t="inlineStr">
@@ -7740,20 +7626,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="T39" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="U39" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -7903,28 +7783,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="M40" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N40" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -7932,12 +7803,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -7971,12 +7839,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W40" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -8038,36 +7903,24 @@
           <t>張蕙宇</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8423,28 +8276,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AB42" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC42" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD42" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -9094,12 +8938,9 @@
           <t>蔡雨筑</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9191,12 +9032,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q46" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R46" s="1" t="inlineStr">
@@ -9225,12 +9063,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="V46" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W46" s="1" t="inlineStr">
@@ -9348,12 +9183,9 @@
 DO2</t>
         </is>
       </c>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -9361,12 +9193,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="M47" s="1" t="inlineStr">
@@ -9411,12 +9240,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S47" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T47" s="1" t="inlineStr">
@@ -9879,12 +9705,9 @@
 DO2</t>
         </is>
       </c>
-      <c r="Y49" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -10065,20 +9888,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="V50" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="W50" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X50" s="1" t="inlineStr">
@@ -10431,12 +10248,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="P52" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q52" s="1" t="inlineStr">
@@ -10687,20 +10501,14 @@
 8:30</t>
         </is>
       </c>
-      <c r="V53" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="W53" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -11490,12 +11298,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>FAC</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -11569,20 +11374,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AC57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -11779,12 +11578,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC58" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -12061,28 +11857,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M60" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -12090,20 +11877,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="O60" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P60" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q60" s="1" t="inlineStr">
@@ -12333,12 +12114,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S61" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T61" s="1" t="inlineStr">
@@ -12480,12 +12258,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -12691,12 +12466,9 @@
 DO2</t>
         </is>
       </c>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -12733,12 +12505,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P63" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -12960,12 +12729,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R64" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -13125,12 +12891,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L65" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M65" s="1" t="inlineStr">
@@ -13149,12 +12912,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O65" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -13392,12 +13152,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="U66" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -13568,12 +13325,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P67" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q67" s="1" t="inlineStr">
@@ -13613,12 +13367,9 @@
 9:19</t>
         </is>
       </c>
-      <c r="V67" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -13686,12 +13437,9 @@
           <t>董雅欣</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -14238,12 +13986,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="V70" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W70" s="1" t="inlineStr">
@@ -14739,20 +14484,14 @@
           <t>李亞韋</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -14787,12 +14526,9 @@
 DO2</t>
         </is>
       </c>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -14981,12 +14717,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="H74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -14994,12 +14727,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -15007,12 +14737,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L74" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M74" s="1" t="inlineStr">
@@ -15128,12 +14855,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
     </row>
@@ -15209,28 +14933,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L75" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M75" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N75" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -15262,12 +14977,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S75" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -15511,12 +15223,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y76" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z76" s="1" t="inlineStr">
@@ -15889,20 +15598,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S78" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T78" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="U78" s="1" t="inlineStr">
@@ -16078,12 +15781,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P79" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -16091,36 +15791,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R79" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="S79" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T79" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="U79" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V79" s="1" t="inlineStr">
@@ -16195,20 +15883,14 @@
           <t>陳玟秀</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -16321,12 +16003,9 @@
 8:38</t>
         </is>
       </c>
-      <c r="U80" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V80" s="1" t="inlineStr">
@@ -16649,12 +16328,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="H82" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -16662,20 +16338,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -16986,20 +16656,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z83" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA83" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AB83" s="1" t="inlineStr">
@@ -17312,36 +16976,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L85" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M85" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N85" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O85" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -17462,12 +17114,9 @@
           <t>張群豔</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17625,12 +17274,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AA86" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
@@ -18011,20 +17657,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="V88" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="W88" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -18061,12 +17701,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AC88" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -18478,20 +18115,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AC90" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD90" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -18633,12 +18264,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="U91" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V91" s="1" t="inlineStr">
@@ -18788,28 +18416,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="M92" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N92" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O92" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -18817,12 +18436,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q92" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -18850,12 +18466,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="W92" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -18863,12 +18476,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y92" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
@@ -18876,12 +18486,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AA92" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
@@ -19212,28 +18819,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="O94" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P94" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q94" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -19241,28 +18839,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S94" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T94" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="U94" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -19270,12 +18859,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W94" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
@@ -19283,12 +18869,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y94" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
@@ -19301,12 +18884,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AB94" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AC94" s="1" t="inlineStr">
@@ -19511,20 +19091,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AB95" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC95" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
@@ -19544,20 +19118,14 @@
           <t>李佩姍</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -19726,12 +19294,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AC96" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD96" s="1" t="inlineStr">
@@ -20025,12 +19590,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="L98" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -20043,12 +19605,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="O98" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -20061,12 +19620,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="R98" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -20146,12 +19702,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD98" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -20353,12 +19906,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD99" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -20457,20 +20007,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="O100" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P100" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -20478,28 +20022,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R100" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="S100" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T100" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>FAC</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -20832,12 +20367,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P102" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q102" s="1" t="inlineStr">
@@ -20856,12 +20388,9 @@
 8:31</t>
         </is>
       </c>
-      <c r="S102" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -20869,12 +20398,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="U102" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="V102" s="1" t="inlineStr">
@@ -21018,44 +20544,29 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="M103" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N103" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O103" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P103" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q103" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -21063,12 +20574,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S103" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T103" s="1" t="inlineStr">
@@ -21218,12 +20726,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="L104" s="1" t="inlineStr">
@@ -21263,12 +20768,9 @@
 9:28</t>
         </is>
       </c>
-      <c r="Q104" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R104" s="1" t="inlineStr">
@@ -22325,12 +21827,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R109" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -22402,20 +21901,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AC109" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD109" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -22430,20 +21923,14 @@
           <t>温雅婷</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -22451,20 +21938,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -22489,12 +21970,9 @@
 9:10</t>
         </is>
       </c>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -22662,28 +22140,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="H111" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -22696,28 +22165,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K111" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L111" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M111" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -22725,20 +22185,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="O111" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P111" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -22996,12 +22450,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W112" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -23030,20 +22481,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AB112" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC112" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr">
@@ -23579,12 +23024,9 @@
 9:19</t>
         </is>
       </c>
-      <c r="O115" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -23597,28 +23039,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R115" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="S115" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T115" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -23914,12 +23347,9 @@
           <t>朱芳頡</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -24007,28 +23437,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="P117" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q117" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R117" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S117" s="1" t="inlineStr">
@@ -24291,36 +23712,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z118" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA118" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB118" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC118" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -24776,20 +24185,14 @@
 8:05</t>
         </is>
       </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -24802,20 +24205,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="L121" s="1" t="inlineStr">
@@ -24860,12 +24257,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R121" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -25057,36 +24451,24 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="P122" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q122" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R122" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="S122" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
@@ -25514,12 +24896,9 @@
 9:38</t>
         </is>
       </c>
-      <c r="U124" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V124" s="1" t="inlineStr">
@@ -25937,12 +25316,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="U126" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V126" s="1" t="inlineStr">
@@ -25963,12 +25339,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y126" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
@@ -26658,12 +26031,9 @@
           <t>李明育</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -26676,20 +26046,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="H130" s="1" t="inlineStr">
@@ -26764,12 +26128,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R130" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S130" s="1" t="inlineStr">
@@ -27190,12 +26551,9 @@
 8:08</t>
         </is>
       </c>
-      <c r="R132" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -27312,20 +26670,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -27353,20 +26705,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -27395,12 +26741,9 @@
 8:13</t>
         </is>
       </c>
-      <c r="S133" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T133" s="1" t="inlineStr">
@@ -27885,12 +27228,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AB135" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -27898,12 +27238,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD135" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
